--- a/grupos/2AEV - Estadisticos 20212.xlsx
+++ b/grupos/2AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="161">
   <si>
     <t>Materia</t>
   </si>
@@ -191,12 +191,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
@@ -260,247 +260,247 @@
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MACIEL</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TAMAYO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MACIEL</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>MONFIL</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>JACOBO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>EDGAR FLORENCIO</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>JUAN DIEGO</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>JOSE DAMIAN</t>
+  </si>
+  <si>
+    <t>MARIA VALERIA</t>
+  </si>
+  <si>
+    <t>DULIAM</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>VICTOR ISRAEL</t>
+  </si>
+  <si>
+    <t>DAVID DANIEL</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>JOSE EDUARDO</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
+    <t>JOSMAR JAHIR</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>ANGEL YAIR</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
     <t>CANTU</t>
   </si>
   <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>MONFIL</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
     <t>MEDINA</t>
   </si>
   <si>
-    <t>SORIA</t>
-  </si>
-  <si>
     <t>ATENOGENES</t>
   </si>
   <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
     <t>ITZEEL GUADALUPE</t>
   </si>
   <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>EDGAR FLORENCIO</t>
-  </si>
-  <si>
-    <t>YOLET</t>
-  </si>
-  <si>
-    <t>JUAN DIEGO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
     <t>ARIEL</t>
   </si>
   <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
-  </si>
-  <si>
-    <t>DAVID DANIEL</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>LUIS ARMANDO</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
     <t>GERSON UZIEL</t>
   </si>
   <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
     <t>RICARDO</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>JOSMAR JAHIR</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>ANGEL YAIR</t>
   </si>
 </sst>
 </file>
@@ -1066,7 +1066,7 @@
         <v>-1</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -1120,7 +1120,7 @@
         <v>-1</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -1143,7 +1143,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>8</v>
@@ -1197,7 +1197,7 @@
         <v>6</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>8</v>
@@ -1220,7 +1220,7 @@
         <v>-1</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1274,7 +1274,7 @@
         <v>-1</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>6</v>
@@ -1297,7 +1297,7 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>9</v>
@@ -1351,7 +1351,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1528,7 +1528,7 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -1582,7 +1582,7 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>7</v>
@@ -1682,7 +1682,7 @@
         <v>-1</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -1759,7 +1759,7 @@
         <v>6</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -1813,7 +1813,7 @@
         <v>6</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>7</v>
@@ -1913,7 +1913,7 @@
         <v>10</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>6</v>
@@ -1967,7 +1967,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>6</v>
@@ -1990,7 +1990,7 @@
         <v>10</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <v>8</v>
@@ -2035,7 +2035,7 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -2055,7 +2055,7 @@
         <v>8</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D18">
         <v>7</v>
@@ -2109,7 +2109,7 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -2132,7 +2132,7 @@
         <v>6</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -2186,7 +2186,7 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>7</v>
@@ -2209,7 +2209,7 @@
         <v>-1</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -2263,7 +2263,7 @@
         <v>-1</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2286,7 +2286,7 @@
         <v>-1</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -2340,7 +2340,7 @@
         <v>-1</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>6</v>
@@ -2363,7 +2363,7 @@
         <v>10</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <v>10</v>
@@ -2417,7 +2417,7 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2440,7 +2440,7 @@
         <v>8</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>8</v>
@@ -2494,7 +2494,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2517,7 +2517,7 @@
         <v>-1</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -2571,7 +2571,7 @@
         <v>-1</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>5</v>
@@ -2594,7 +2594,7 @@
         <v>10</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D25">
         <v>10</v>
@@ -2648,7 +2648,7 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2671,7 +2671,7 @@
         <v>10</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D26">
         <v>8</v>
@@ -2725,7 +2725,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2748,7 +2748,7 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D27">
         <v>8</v>
@@ -2802,7 +2802,7 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V27">
         <v>8</v>
@@ -2825,7 +2825,7 @@
         <v>-1</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -2879,7 +2879,7 @@
         <v>-1</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>6</v>
@@ -2979,7 +2979,7 @@
         <v>7</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D30">
         <v>7</v>
@@ -3033,7 +3033,7 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V30">
         <v>7</v>
@@ -3056,7 +3056,7 @@
         <v>8</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D31">
         <v>8</v>
@@ -3110,7 +3110,7 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>8</v>
@@ -3133,7 +3133,7 @@
         <v>10</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D32">
         <v>8</v>
@@ -3187,7 +3187,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>8</v>
@@ -3210,7 +3210,7 @@
         <v>10</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D33">
         <v>7</v>
@@ -3264,7 +3264,7 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>7</v>
@@ -3441,7 +3441,7 @@
         <v>7</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>7</v>
@@ -3495,7 +3495,7 @@
         <v>7</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V36">
         <v>7</v>
@@ -3518,7 +3518,7 @@
         <v>6</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D37">
         <v>8</v>
@@ -3572,7 +3572,7 @@
         <v>6</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V37">
         <v>8</v>
@@ -3595,7 +3595,7 @@
         <v>10</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D38">
         <v>7</v>
@@ -3649,7 +3649,7 @@
         <v>10</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>7</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
@@ -3803,27 +3803,30 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>9</v>
+      </c>
       <c r="I2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>88.89</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -3832,25 +3835,25 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>11.11</v>
+        <v>47.22</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>27.78</v>
       </c>
       <c r="H3">
+        <v>6.2</v>
+      </c>
+      <c r="I3">
         <v>9</v>
       </c>
-      <c r="I3">
-        <v>32</v>
-      </c>
       <c r="J3">
-        <v>88.89</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3988,7 +3991,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4026,13 +4029,13 @@
         <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4046,13 +4049,13 @@
         <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4066,7 +4069,7 @@
         <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4083,16 +4086,16 @@
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4103,93 +4106,93 @@
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920002</v>
+        <v>21330051920003</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920003</v>
+        <v>21330051920005</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920003</v>
+        <v>21330051920005</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920004</v>
+        <v>21330051920006</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
         <v>57</v>
@@ -4197,39 +4200,39 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920005</v>
+        <v>21330051920006</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920005</v>
+        <v>21330051920007</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
         <v>57</v>
@@ -4237,19 +4240,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920006</v>
+        <v>21330051920007</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
         <v>58</v>
@@ -4257,139 +4260,139 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920006</v>
+        <v>21330051920007</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920006</v>
+        <v>21330051920008</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920007</v>
+        <v>20330051920049</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920007</v>
+        <v>20330051920049</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920007</v>
+        <v>21330051920380</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
         <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920008</v>
+        <v>21330051920380</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920008</v>
+        <v>21330051920010</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
         <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
         <v>57</v>
@@ -4397,79 +4400,79 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920049</v>
+        <v>21330051920355</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
         <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920049</v>
+        <v>21330051920355</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
         <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920380</v>
+        <v>20330051920078</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920380</v>
+        <v>21330051920011</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
         <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
         <v>57</v>
@@ -4477,139 +4480,139 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920380</v>
+        <v>21330051920013</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E25" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920010</v>
+        <v>21330051920014</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920010</v>
+        <v>21330051920014</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920355</v>
+        <v>20330051920019</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920355</v>
+        <v>20330051920019</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920078</v>
+        <v>20330051920391</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="D30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>20330051920078</v>
+        <v>21330051920015</v>
       </c>
       <c r="B31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" t="s">
         <v>78</v>
-      </c>
-      <c r="C31" t="s">
-        <v>76</v>
       </c>
       <c r="D31" t="s">
         <v>138</v>
       </c>
       <c r="E31" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
         <v>57</v>
@@ -4617,13 +4620,13 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920011</v>
+        <v>21330051920016</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s">
         <v>139</v>
@@ -4632,24 +4635,24 @@
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920011</v>
+        <v>21330051920017</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
         <v>57</v>
@@ -4657,33 +4660,33 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920012</v>
+        <v>21330051920017</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="D34" t="s">
         <v>140</v>
       </c>
       <c r="E34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F34" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920013</v>
+        <v>20330051920022</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C35" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D35" t="s">
         <v>141</v>
@@ -4692,24 +4695,24 @@
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920013</v>
+        <v>21330051920379</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D36" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E36" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F36" t="s">
         <v>57</v>
@@ -4717,116 +4720,116 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>21330051920014</v>
+        <v>21330051920385</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C37" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>21330051920014</v>
+        <v>21330051920385</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D38" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F38" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920014</v>
+        <v>21330051920018</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D39" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E39" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>20330051920019</v>
+        <v>21330051920356</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D40" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>20330051920019</v>
+        <v>21330051920356</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C41" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D41" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E41" t="s">
         <v>6</v>
       </c>
       <c r="F41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>20330051920019</v>
+        <v>21330051920356</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C42" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D42" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E42" t="s">
         <v>5</v>
@@ -4837,39 +4840,39 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>20330051920391</v>
+        <v>21330051920021</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D43" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>20330051920391</v>
+        <v>21330051920023</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C44" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D44" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E44" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F44" t="s">
         <v>57</v>
@@ -4877,19 +4880,19 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>21330051920015</v>
+        <v>21330051920023</v>
       </c>
       <c r="B45" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C45" t="s">
         <v>78</v>
       </c>
       <c r="D45" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E45" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F45" t="s">
         <v>58</v>
@@ -4897,99 +4900,99 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>21330051920015</v>
+        <v>21330051920023</v>
       </c>
       <c r="B46" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C46" t="s">
         <v>78</v>
       </c>
       <c r="D46" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F46" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>21330051920016</v>
+        <v>21330051920025</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D47" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>21330051920016</v>
+        <v>21330051920025</v>
       </c>
       <c r="B48" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C48" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D48" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E48" t="s">
         <v>6</v>
       </c>
       <c r="F48" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>21330051920017</v>
+        <v>21330051920026</v>
       </c>
       <c r="B49" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C49" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="D49" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>21330051920017</v>
+        <v>21330051920027</v>
       </c>
       <c r="B50" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C50" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D50" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E50" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F50" t="s">
         <v>57</v>
@@ -4997,641 +5000,101 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>21330051920017</v>
+        <v>21330051920028</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C51" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D51" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E51" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F51" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>20330051920022</v>
+        <v>21330051920393</v>
       </c>
       <c r="B52" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C52" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D52" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
       </c>
       <c r="F52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>20330051920022</v>
+        <v>21330051920393</v>
       </c>
       <c r="B53" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C53" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D53" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E53" t="s">
         <v>6</v>
       </c>
       <c r="F53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>21330051920379</v>
+        <v>21330051920393</v>
       </c>
       <c r="B54" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C54" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D54" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E54" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F54" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>21330051920379</v>
+        <v>21330051920393</v>
       </c>
       <c r="B55" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C55" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D55" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E55" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920385</v>
-      </c>
-      <c r="B56" t="s">
-        <v>88</v>
-      </c>
-      <c r="C56" t="s">
-        <v>117</v>
-      </c>
-      <c r="D56" t="s">
-        <v>150</v>
-      </c>
-      <c r="E56" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920385</v>
-      </c>
-      <c r="B57" t="s">
-        <v>88</v>
-      </c>
-      <c r="C57" t="s">
-        <v>117</v>
-      </c>
-      <c r="D57" t="s">
-        <v>150</v>
-      </c>
-      <c r="E57" t="s">
-        <v>6</v>
-      </c>
-      <c r="F57" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920385</v>
-      </c>
-      <c r="B58" t="s">
-        <v>88</v>
-      </c>
-      <c r="C58" t="s">
-        <v>117</v>
-      </c>
-      <c r="D58" t="s">
-        <v>150</v>
-      </c>
-      <c r="E58" t="s">
-        <v>5</v>
-      </c>
-      <c r="F58" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920018</v>
-      </c>
-      <c r="B59" t="s">
-        <v>89</v>
-      </c>
-      <c r="C59" t="s">
-        <v>118</v>
-      </c>
-      <c r="D59" t="s">
-        <v>151</v>
-      </c>
-      <c r="E59" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920018</v>
-      </c>
-      <c r="B60" t="s">
-        <v>89</v>
-      </c>
-      <c r="C60" t="s">
-        <v>118</v>
-      </c>
-      <c r="D60" t="s">
-        <v>151</v>
-      </c>
-      <c r="E60" t="s">
-        <v>6</v>
-      </c>
-      <c r="F60" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920356</v>
-      </c>
-      <c r="B61" t="s">
-        <v>90</v>
-      </c>
-      <c r="C61" t="s">
-        <v>80</v>
-      </c>
-      <c r="D61" t="s">
-        <v>152</v>
-      </c>
-      <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920356</v>
-      </c>
-      <c r="B62" t="s">
-        <v>90</v>
-      </c>
-      <c r="C62" t="s">
-        <v>80</v>
-      </c>
-      <c r="D62" t="s">
-        <v>152</v>
-      </c>
-      <c r="E62" t="s">
-        <v>6</v>
-      </c>
-      <c r="F62" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920356</v>
-      </c>
-      <c r="B63" t="s">
-        <v>90</v>
-      </c>
-      <c r="C63" t="s">
-        <v>80</v>
-      </c>
-      <c r="D63" t="s">
-        <v>152</v>
-      </c>
-      <c r="E63" t="s">
-        <v>5</v>
-      </c>
-      <c r="F63" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920019</v>
-      </c>
-      <c r="B64" t="s">
-        <v>91</v>
-      </c>
-      <c r="C64" t="s">
-        <v>119</v>
-      </c>
-      <c r="D64" t="s">
-        <v>153</v>
-      </c>
-      <c r="E64" t="s">
-        <v>6</v>
-      </c>
-      <c r="F64" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920021</v>
-      </c>
-      <c r="B65" t="s">
-        <v>92</v>
-      </c>
-      <c r="C65" t="s">
-        <v>120</v>
-      </c>
-      <c r="D65" t="s">
-        <v>154</v>
-      </c>
-      <c r="E65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920021</v>
-      </c>
-      <c r="B66" t="s">
-        <v>92</v>
-      </c>
-      <c r="C66" t="s">
-        <v>120</v>
-      </c>
-      <c r="D66" t="s">
-        <v>154</v>
-      </c>
-      <c r="E66" t="s">
-        <v>6</v>
-      </c>
-      <c r="F66" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920022</v>
-      </c>
-      <c r="B67" t="s">
-        <v>93</v>
-      </c>
-      <c r="C67" t="s">
-        <v>121</v>
-      </c>
-      <c r="D67" t="s">
-        <v>155</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920023</v>
-      </c>
-      <c r="B68" t="s">
-        <v>94</v>
-      </c>
-      <c r="C68" t="s">
-        <v>78</v>
-      </c>
-      <c r="D68" t="s">
-        <v>156</v>
-      </c>
-      <c r="E68" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920023</v>
-      </c>
-      <c r="B69" t="s">
-        <v>94</v>
-      </c>
-      <c r="C69" t="s">
-        <v>78</v>
-      </c>
-      <c r="D69" t="s">
-        <v>156</v>
-      </c>
-      <c r="E69" t="s">
-        <v>6</v>
-      </c>
-      <c r="F69" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>21330051920023</v>
-      </c>
-      <c r="B70" t="s">
-        <v>94</v>
-      </c>
-      <c r="C70" t="s">
-        <v>78</v>
-      </c>
-      <c r="D70" t="s">
-        <v>156</v>
-      </c>
-      <c r="E70" t="s">
-        <v>5</v>
-      </c>
-      <c r="F70" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>21330051920025</v>
-      </c>
-      <c r="B71" t="s">
-        <v>95</v>
-      </c>
-      <c r="C71" t="s">
-        <v>122</v>
-      </c>
-      <c r="D71" t="s">
-        <v>157</v>
-      </c>
-      <c r="E71" t="s">
-        <v>8</v>
-      </c>
-      <c r="F71" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>21330051920025</v>
-      </c>
-      <c r="B72" t="s">
-        <v>95</v>
-      </c>
-      <c r="C72" t="s">
-        <v>122</v>
-      </c>
-      <c r="D72" t="s">
-        <v>157</v>
-      </c>
-      <c r="E72" t="s">
-        <v>6</v>
-      </c>
-      <c r="F72" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>21330051920026</v>
-      </c>
-      <c r="B73" t="s">
-        <v>96</v>
-      </c>
-      <c r="C73" t="s">
-        <v>78</v>
-      </c>
-      <c r="D73" t="s">
-        <v>158</v>
-      </c>
-      <c r="E73" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>21330051920026</v>
-      </c>
-      <c r="B74" t="s">
-        <v>96</v>
-      </c>
-      <c r="C74" t="s">
-        <v>78</v>
-      </c>
-      <c r="D74" t="s">
-        <v>158</v>
-      </c>
-      <c r="E74" t="s">
-        <v>6</v>
-      </c>
-      <c r="F74" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>21330051920027</v>
-      </c>
-      <c r="B75" t="s">
-        <v>97</v>
-      </c>
-      <c r="C75" t="s">
-        <v>123</v>
-      </c>
-      <c r="D75" t="s">
-        <v>141</v>
-      </c>
-      <c r="E75" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>21330051920027</v>
-      </c>
-      <c r="B76" t="s">
-        <v>97</v>
-      </c>
-      <c r="C76" t="s">
-        <v>123</v>
-      </c>
-      <c r="D76" t="s">
-        <v>141</v>
-      </c>
-      <c r="E76" t="s">
-        <v>6</v>
-      </c>
-      <c r="F76" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920028</v>
-      </c>
-      <c r="B77" t="s">
-        <v>98</v>
-      </c>
-      <c r="C77" t="s">
-        <v>124</v>
-      </c>
-      <c r="D77" t="s">
-        <v>159</v>
-      </c>
-      <c r="E77" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>21330051920028</v>
-      </c>
-      <c r="B78" t="s">
-        <v>98</v>
-      </c>
-      <c r="C78" t="s">
-        <v>124</v>
-      </c>
-      <c r="D78" t="s">
-        <v>159</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>21330051920393</v>
-      </c>
-      <c r="B79" t="s">
-        <v>99</v>
-      </c>
-      <c r="C79" t="s">
-        <v>125</v>
-      </c>
-      <c r="D79" t="s">
-        <v>160</v>
-      </c>
-      <c r="E79" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>21330051920393</v>
-      </c>
-      <c r="B80" t="s">
-        <v>99</v>
-      </c>
-      <c r="C80" t="s">
-        <v>125</v>
-      </c>
-      <c r="D80" t="s">
-        <v>160</v>
-      </c>
-      <c r="E80" t="s">
-        <v>6</v>
-      </c>
-      <c r="F80" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>21330051920393</v>
-      </c>
-      <c r="B81" t="s">
-        <v>99</v>
-      </c>
-      <c r="C81" t="s">
-        <v>125</v>
-      </c>
-      <c r="D81" t="s">
-        <v>160</v>
-      </c>
-      <c r="E81" t="s">
-        <v>5</v>
-      </c>
-      <c r="F81" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>21330051920393</v>
-      </c>
-      <c r="B82" t="s">
-        <v>99</v>
-      </c>
-      <c r="C82" t="s">
-        <v>125</v>
-      </c>
-      <c r="D82" t="s">
-        <v>160</v>
-      </c>
-      <c r="E82" t="s">
-        <v>10</v>
-      </c>
-      <c r="F82" t="s">
         <v>60</v>
       </c>
     </row>
@@ -5671,13 +5134,13 @@
         <v>21330051920393</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D2" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -5694,7 +5157,7 @@
         <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -5702,16 +5165,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920002</v>
+        <v>21330051920007</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
         <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -5719,16 +5182,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920006</v>
+        <v>21330051920356</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -5736,16 +5199,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920007</v>
+        <v>21330051920023</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -5753,135 +5216,135 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920380</v>
+        <v>21330051920002</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920014</v>
+        <v>21330051920005</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920019</v>
+        <v>21330051920006</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920017</v>
+        <v>20330051920049</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920385</v>
+        <v>21330051920380</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920356</v>
+        <v>21330051920355</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920023</v>
+        <v>21330051920014</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920003</v>
+        <v>20330051920019</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -5889,16 +5352,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920005</v>
+        <v>21330051920017</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -5906,16 +5369,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920008</v>
+        <v>21330051920385</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -5923,16 +5386,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920049</v>
+        <v>21330051920025</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -5940,223 +5403,223 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920010</v>
+        <v>21330051920003</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920355</v>
+        <v>21330051920008</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920078</v>
+        <v>21330051920010</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920011</v>
+        <v>20330051920078</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920013</v>
+        <v>21330051920011</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920391</v>
+        <v>21330051920013</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920015</v>
+        <v>20330051920391</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920016</v>
+        <v>21330051920015</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920022</v>
+        <v>21330051920016</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920379</v>
+        <v>20330051920022</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D27" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920018</v>
+        <v>21330051920379</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D28" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920021</v>
+        <v>21330051920018</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920025</v>
+        <v>21330051920021</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -6164,16 +5627,16 @@
         <v>21330051920026</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
         <v>78</v>
       </c>
       <c r="D31" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -6181,16 +5644,16 @@
         <v>21330051920027</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -6198,16 +5661,16 @@
         <v>21330051920028</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -6218,13 +5681,13 @@
         <v>70</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="D34" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -6232,16 +5695,16 @@
         <v>21330051920012</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
         <v>76</v>
       </c>
       <c r="D35" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -6249,16 +5712,16 @@
         <v>21330051920019</v>
       </c>
       <c r="B36" t="s">
-        <v>91</v>
+        <v>152</v>
       </c>
       <c r="C36" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="D36" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6266,16 +5729,16 @@
         <v>21330051920022</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="D37" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6285,7 +5748,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6317,22 +5780,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920003</v>
+        <v>21330051920005</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -6340,22 +5803,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920003</v>
+        <v>21330051920005</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -6363,22 +5826,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920005</v>
+        <v>20330051920049</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -6386,22 +5849,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920005</v>
+        <v>20330051920049</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -6409,22 +5872,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920008</v>
+        <v>21330051920355</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -6432,22 +5895,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920008</v>
+        <v>21330051920355</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -6455,45 +5918,45 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920049</v>
+        <v>21330051920016</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920049</v>
+        <v>21330051920016</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -6501,45 +5964,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920010</v>
+        <v>20330051920022</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920010</v>
+        <v>20330051920022</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -6547,19 +6010,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920355</v>
+        <v>21330051920018</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
         <v>57</v>
@@ -6570,45 +6033,45 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920355</v>
+        <v>21330051920018</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920078</v>
+        <v>21330051920025</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -6616,22 +6079,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920078</v>
+        <v>21330051920025</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -6639,45 +6102,45 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920011</v>
+        <v>21330051920026</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920011</v>
+        <v>21330051920026</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G17">
         <v>-1</v>
@@ -6685,19 +6148,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920013</v>
+        <v>21330051920003</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
         <v>57</v>
@@ -6708,22 +6171,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920013</v>
+        <v>21330051920008</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G19">
         <v>-1</v>
@@ -6731,19 +6194,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920391</v>
+        <v>21330051920010</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
         <v>57</v>
@@ -6754,22 +6217,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920391</v>
+        <v>20330051920078</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G21">
         <v>-1</v>
@@ -6777,19 +6240,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920015</v>
+        <v>21330051920011</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
         <v>57</v>
@@ -6800,22 +6263,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920015</v>
+        <v>21330051920013</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G23">
         <v>-1</v>
@@ -6823,19 +6286,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920016</v>
+        <v>20330051920391</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
         <v>57</v>
@@ -6846,22 +6309,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920016</v>
+        <v>21330051920015</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G25">
         <v>-1</v>
@@ -6869,19 +6332,19 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920022</v>
+        <v>21330051920379</v>
       </c>
       <c r="B26" t="s">
         <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
         <v>57</v>
@@ -6892,22 +6355,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920022</v>
+        <v>21330051920021</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G27">
         <v>-1</v>
@@ -6915,19 +6378,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051920379</v>
+        <v>21330051920027</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F28" t="s">
         <v>57</v>
@@ -6938,346 +6401,24 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920379</v>
+        <v>21330051920028</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920021</v>
-      </c>
-      <c r="B30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" t="s">
-        <v>154</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920021</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D31" t="s">
-        <v>154</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>58</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920025</v>
-      </c>
-      <c r="B32" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" t="s">
-        <v>122</v>
-      </c>
-      <c r="D32" t="s">
-        <v>157</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>57</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920025</v>
-      </c>
-      <c r="B33" t="s">
-        <v>95</v>
-      </c>
-      <c r="C33" t="s">
-        <v>122</v>
-      </c>
-      <c r="D33" t="s">
-        <v>157</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>58</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920026</v>
-      </c>
-      <c r="B34" t="s">
-        <v>96</v>
-      </c>
-      <c r="C34" t="s">
-        <v>78</v>
-      </c>
-      <c r="D34" t="s">
-        <v>158</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>57</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920026</v>
-      </c>
-      <c r="B35" t="s">
-        <v>96</v>
-      </c>
-      <c r="C35" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" t="s">
-        <v>158</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>58</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>21330051920027</v>
-      </c>
-      <c r="B36" t="s">
-        <v>97</v>
-      </c>
-      <c r="C36" t="s">
-        <v>123</v>
-      </c>
-      <c r="D36" t="s">
-        <v>141</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>57</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>21330051920027</v>
-      </c>
-      <c r="B37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C37" t="s">
-        <v>123</v>
-      </c>
-      <c r="D37" t="s">
-        <v>141</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>58</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>21330051920028</v>
-      </c>
-      <c r="B38" t="s">
-        <v>98</v>
-      </c>
-      <c r="C38" t="s">
-        <v>124</v>
-      </c>
-      <c r="D38" t="s">
-        <v>159</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>57</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>21330051920028</v>
-      </c>
-      <c r="B39" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" t="s">
-        <v>124</v>
-      </c>
-      <c r="D39" t="s">
-        <v>159</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>58</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>21330051920004</v>
-      </c>
-      <c r="B40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" t="s">
-        <v>102</v>
-      </c>
-      <c r="D40" t="s">
-        <v>129</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>57</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920012</v>
-      </c>
-      <c r="B41" t="s">
-        <v>80</v>
-      </c>
-      <c r="C41" t="s">
-        <v>76</v>
-      </c>
-      <c r="D41" t="s">
-        <v>140</v>
-      </c>
-      <c r="E41" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" t="s">
-        <v>57</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>21330051920019</v>
-      </c>
-      <c r="B42" t="s">
-        <v>91</v>
-      </c>
-      <c r="C42" t="s">
-        <v>119</v>
-      </c>
-      <c r="D42" t="s">
-        <v>153</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>57</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>21330051920022</v>
-      </c>
-      <c r="B43" t="s">
-        <v>93</v>
-      </c>
-      <c r="C43" t="s">
-        <v>121</v>
-      </c>
-      <c r="D43" t="s">
-        <v>155</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G43">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2AEV - Estadisticos 20212.xlsx
+++ b/grupos/2AEV - Estadisticos 20212.xlsx
@@ -1010,7 +1010,7 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -1087,7 +1087,7 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1164,7 +1164,7 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1200,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>-1</v>
@@ -1241,7 +1241,7 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1318,7 +1318,7 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1395,7 +1395,7 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1431,7 +1431,7 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>-1</v>
@@ -1472,7 +1472,7 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1549,7 +1549,7 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1626,7 +1626,7 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1703,7 +1703,7 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1780,7 +1780,7 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1857,7 +1857,7 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1934,7 +1934,7 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -1970,7 +1970,7 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>-1</v>
@@ -2008,7 +2008,7 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -2076,7 +2076,7 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2153,7 +2153,7 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2230,7 +2230,7 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2307,7 +2307,7 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2384,7 +2384,7 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2461,7 +2461,7 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2615,7 +2615,7 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -2651,7 +2651,7 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>-1</v>
@@ -2692,7 +2692,7 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2769,7 +2769,7 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2846,7 +2846,7 @@
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -2923,7 +2923,7 @@
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -3000,7 +3000,7 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -3036,7 +3036,7 @@
         <v>6</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>-1</v>
@@ -3077,7 +3077,7 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -3154,7 +3154,7 @@
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3231,7 +3231,7 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3267,7 +3267,7 @@
         <v>8</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3308,7 +3308,7 @@
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3344,7 +3344,7 @@
         <v>-1</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W34">
         <v>-1</v>
@@ -3385,7 +3385,7 @@
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3421,7 +3421,7 @@
         <v>-1</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>-1</v>
@@ -3462,7 +3462,7 @@
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3539,7 +3539,7 @@
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
         <v>-1</v>
@@ -3616,7 +3616,7 @@
         <v>-1</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
         <v>-1</v>
@@ -3652,7 +3652,7 @@
         <v>8</v>
       </c>
       <c r="V38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W38">
         <v>-1</v>
@@ -3693,7 +3693,7 @@
         <v>-1</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K39">
         <v>-1</v>
@@ -3975,7 +3975,7 @@
         <v>8.33</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/2AEV - Estadisticos 20212.xlsx
+++ b/grupos/2AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="161">
   <si>
     <t>Materia</t>
   </si>
@@ -197,12 +197,12 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
@@ -239,88 +239,190 @@
     <t>COBOS</t>
   </si>
   <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>MONFIL</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>EDGAR FLORENCIO</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>JOSE DAMIAN</t>
+  </si>
+  <si>
+    <t>MARIA VALERIA</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>VICTOR ISRAEL</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>JOSE EDUARDO</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>ANGEL YAIR</t>
+  </si>
+  <si>
     <t>COSCAHUA</t>
   </si>
   <si>
     <t>CUATRA</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MACIEL</t>
   </si>
   <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
     <t>PERALTA</t>
   </si>
   <si>
-    <t>PELLICO</t>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
+    <t>SANTIAGO</t>
   </si>
   <si>
     <t>TAMAYO</t>
   </si>
   <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
+    <t>CANTU</t>
   </si>
   <si>
     <t>TZOYONTLE</t>
@@ -329,76 +431,37 @@
     <t>COYOHUA</t>
   </si>
   <si>
-    <t>MONFIL</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
     <t>JACOBO</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
     <t>CORTES</t>
   </si>
   <si>
     <t>VILLA</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
     <t>GALLARDO</t>
   </si>
   <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
     <t>SORIA</t>
   </si>
   <si>
+    <t>ATENOGENES</t>
+  </si>
+  <si>
     <t>VARGAS</t>
   </si>
   <si>
     <t>COXCAHUA</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>EDGAR FLORENCIO</t>
-  </si>
-  <si>
-    <t>YOLET</t>
+    <t>ITZEEL GUADALUPE</t>
   </si>
   <si>
     <t>JUAN DIEGO</t>
@@ -407,100 +470,37 @@
     <t>RAFAEL</t>
   </si>
   <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
     <t>DULIAM</t>
   </si>
   <si>
     <t>ANDRES</t>
   </si>
   <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
+    <t>ARIEL</t>
   </si>
   <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
-    <t>VICTOR ISRAEL</t>
-  </si>
-  <si>
     <t>DAVID DANIEL</t>
   </si>
   <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
     <t>MIGUEL</t>
   </si>
   <si>
-    <t>LUIS ARMANDO</t>
-  </si>
-  <si>
     <t>CARLOS</t>
   </si>
   <si>
-    <t>OSCAR</t>
+    <t>GERSON UZIEL</t>
   </si>
   <si>
     <t>JESUS EMMANUEL</t>
   </si>
   <si>
-    <t>NEMESIO NAHIM</t>
+    <t>RICARDO</t>
   </si>
   <si>
     <t>JOSMAR JAHIR</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>ANGEL YAIR</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CANTU</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>ATENOGENES</t>
-  </si>
-  <si>
-    <t>ITZEEL GUADALUPE</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>GERSON UZIEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
   </si>
 </sst>
 </file>
@@ -989,7 +989,7 @@
         <v>-1</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -1007,7 +1007,7 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>7</v>
@@ -1019,7 +1019,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1043,7 +1043,7 @@
         <v>-1</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -1072,7 +1072,7 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -1084,19 +1084,19 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1126,7 +1126,7 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -1158,10 +1158,10 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>9</v>
@@ -1170,10 +1170,10 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1209,7 +1209,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1217,7 +1217,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1238,7 +1238,7 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1250,7 +1250,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1271,7 +1271,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>5</v>
@@ -1312,22 +1312,22 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1363,7 +1363,7 @@
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1374,7 +1374,7 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -1392,7 +1392,7 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>8</v>
@@ -1404,7 +1404,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1428,7 +1428,7 @@
         <v>6</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>8</v>
@@ -1440,7 +1440,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1451,7 +1451,7 @@
         <v>-1</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>7</v>
@@ -1469,7 +1469,7 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>7</v>
@@ -1481,7 +1481,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1505,7 +1505,7 @@
         <v>-1</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -1534,7 +1534,7 @@
         <v>7</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F11">
         <v>7</v>
@@ -1543,22 +1543,22 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1582,16 +1582,16 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>7</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1605,13 +1605,13 @@
         <v>10</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>8</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F12">
         <v>10</v>
@@ -1620,22 +1620,22 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1656,16 +1656,16 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>8</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1700,7 +1700,7 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>6</v>
@@ -1712,7 +1712,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1774,10 +1774,10 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>7</v>
@@ -1786,10 +1786,10 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1822,10 +1822,10 @@
         <v>-1</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1836,7 +1836,7 @@
         <v>8</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>8</v>
@@ -1851,10 +1851,10 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>7</v>
@@ -1866,7 +1866,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1887,10 +1887,10 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
         <v>8</v>
@@ -1919,7 +1919,7 @@
         <v>6</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F16">
         <v>10</v>
@@ -1928,22 +1928,22 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1967,19 +1967,19 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>7</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1996,25 +1996,25 @@
         <v>8</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G17">
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2041,10 +2041,10 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2070,22 +2070,22 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2106,7 +2106,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>6</v>
@@ -2115,13 +2115,13 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2147,10 +2147,10 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>6</v>
@@ -2162,7 +2162,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2183,7 +2183,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>6</v>
@@ -2227,7 +2227,7 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -2239,7 +2239,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2304,7 +2304,7 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>6</v>
@@ -2316,7 +2316,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2352,7 +2352,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2369,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F22">
         <v>10</v>
@@ -2378,22 +2378,22 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2417,13 +2417,13 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>10</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2455,10 +2455,10 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>7</v>
@@ -2467,10 +2467,10 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2494,7 +2494,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2523,7 +2523,7 @@
         <v>5</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -2535,19 +2535,19 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2577,7 +2577,7 @@
         <v>5</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -2600,7 +2600,7 @@
         <v>10</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F25">
         <v>10</v>
@@ -2609,22 +2609,22 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J25">
         <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2645,7 +2645,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>8</v>
@@ -2654,13 +2654,13 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2686,10 +2686,10 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
         <v>8</v>
@@ -2698,10 +2698,10 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2725,7 +2725,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2737,7 +2737,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2754,7 +2754,7 @@
         <v>8</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F27">
         <v>10</v>
@@ -2763,22 +2763,22 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
         <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2799,22 +2799,22 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>8</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2843,7 +2843,7 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
         <v>6</v>
@@ -2855,7 +2855,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2899,10 +2899,10 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>6</v>
@@ -2917,10 +2917,10 @@
         <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <v>6</v>
@@ -2932,7 +2932,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2953,10 +2953,10 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V29">
         <v>6</v>
@@ -2985,7 +2985,7 @@
         <v>7</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F30">
         <v>10</v>
@@ -2994,22 +2994,22 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
         <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3033,13 +3033,13 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V30">
         <v>8</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -3071,22 +3071,22 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3107,7 +3107,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>7</v>
@@ -3116,13 +3116,13 @@
         <v>8</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3139,7 +3139,7 @@
         <v>8</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F32">
         <v>10</v>
@@ -3148,22 +3148,22 @@
         <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
         <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3187,19 +3187,19 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>8</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X32">
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3225,22 +3225,22 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
         <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3276,7 +3276,7 @@
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3284,10 +3284,10 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D34">
         <v>8</v>
@@ -3302,10 +3302,10 @@
         <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>6</v>
@@ -3314,10 +3314,10 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3338,10 +3338,10 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -3353,7 +3353,7 @@
         <v>10</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3364,13 +3364,13 @@
         <v>8</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D35">
         <v>8</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F35">
         <v>10</v>
@@ -3379,22 +3379,22 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
         <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3415,22 +3415,22 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>9</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3459,7 +3459,7 @@
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
         <v>7</v>
@@ -3471,7 +3471,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3507,7 +3507,7 @@
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3533,10 +3533,10 @@
         <v>6</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J37">
         <v>7</v>
@@ -3548,7 +3548,7 @@
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3572,7 +3572,7 @@
         <v>6</v>
       </c>
       <c r="U37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V37">
         <v>8</v>
@@ -3601,7 +3601,7 @@
         <v>7</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F38">
         <v>10</v>
@@ -3610,22 +3610,22 @@
         <v>8</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J38">
         <v>8</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3655,7 +3655,7 @@
         <v>8</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>10</v>
@@ -3669,10 +3669,10 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D39">
         <v>6</v>
@@ -3684,13 +3684,13 @@
         <v>7</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J39">
         <v>6</v>
@@ -3702,7 +3702,7 @@
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3723,10 +3723,10 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V39">
         <v>6</v>
@@ -3738,7 +3738,7 @@
         <v>7</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3803,25 +3803,25 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>11.11</v>
+        <v>38.89</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J2">
-        <v>88.89</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3835,30 +3835,30 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>47.22</v>
+        <v>50</v>
       </c>
       <c r="G3">
-        <v>27.78</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -3867,30 +3867,30 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4">
+        <v>13</v>
+      </c>
+      <c r="F4">
+        <v>63.89</v>
+      </c>
+      <c r="G4">
+        <v>36.11</v>
+      </c>
+      <c r="H4">
+        <v>6.7</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>66.67</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>8.5</v>
-      </c>
-      <c r="I4">
-        <v>12</v>
-      </c>
-      <c r="J4">
-        <v>33.33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -3899,25 +3899,25 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>69.44</v>
+        <v>77.78</v>
       </c>
       <c r="G5">
-        <v>27.78</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>2.78</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3943,7 +3943,7 @@
         <v>17.14</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3991,7 +3991,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4029,7 +4029,7 @@
         <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4049,47 +4049,47 @@
         <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920001</v>
+        <v>21330051920002</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920002</v>
+        <v>21330051920003</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4100,36 +4100,36 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920002</v>
+        <v>21330051920005</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920003</v>
+        <v>21330051920006</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4140,16 +4140,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920005</v>
+        <v>21330051920007</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4160,36 +4160,36 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920005</v>
+        <v>21330051920007</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920006</v>
+        <v>21330051920380</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4200,36 +4200,36 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920006</v>
+        <v>21330051920380</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920007</v>
+        <v>21330051920010</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4240,56 +4240,56 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920007</v>
+        <v>21330051920355</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920007</v>
+        <v>21330051920013</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920008</v>
+        <v>21330051920014</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -4300,116 +4300,116 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920049</v>
+        <v>21330051920014</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920049</v>
+        <v>20330051920019</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920380</v>
+        <v>20330051920019</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920380</v>
+        <v>21330051920015</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920010</v>
+        <v>21330051920017</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920355</v>
+        <v>20330051920022</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -4420,56 +4420,56 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920355</v>
+        <v>21330051920385</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920078</v>
+        <v>21330051920385</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="D23" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920011</v>
+        <v>21330051920356</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -4480,16 +4480,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920013</v>
+        <v>21330051920023</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -4500,16 +4500,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920014</v>
+        <v>21330051920026</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -4520,582 +4520,42 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920014</v>
+        <v>21330051920028</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="E27" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920019</v>
+        <v>21330051920393</v>
       </c>
       <c r="B28" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920019</v>
-      </c>
-      <c r="B29" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" t="s">
-        <v>136</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920391</v>
-      </c>
-      <c r="B30" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" t="s">
-        <v>110</v>
-      </c>
-      <c r="D30" t="s">
-        <v>137</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920015</v>
-      </c>
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" t="s">
-        <v>78</v>
-      </c>
-      <c r="D31" t="s">
-        <v>138</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920016</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" t="s">
-        <v>111</v>
-      </c>
-      <c r="D32" t="s">
-        <v>139</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920017</v>
-      </c>
-      <c r="B33" t="s">
-        <v>83</v>
-      </c>
-      <c r="C33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" t="s">
-        <v>140</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920017</v>
-      </c>
-      <c r="B34" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" t="s">
-        <v>112</v>
-      </c>
-      <c r="D34" t="s">
-        <v>140</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920022</v>
-      </c>
-      <c r="B35" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" t="s">
-        <v>112</v>
-      </c>
-      <c r="D35" t="s">
-        <v>141</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920379</v>
-      </c>
-      <c r="B36" t="s">
-        <v>86</v>
-      </c>
-      <c r="C36" t="s">
-        <v>113</v>
-      </c>
-      <c r="D36" t="s">
-        <v>142</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920385</v>
-      </c>
-      <c r="B37" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" t="s">
-        <v>114</v>
-      </c>
-      <c r="D37" t="s">
-        <v>143</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920385</v>
-      </c>
-      <c r="B38" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" t="s">
-        <v>114</v>
-      </c>
-      <c r="D38" t="s">
-        <v>143</v>
-      </c>
-      <c r="E38" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920018</v>
-      </c>
-      <c r="B39" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" t="s">
-        <v>115</v>
-      </c>
-      <c r="D39" t="s">
-        <v>144</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920356</v>
-      </c>
-      <c r="B40" t="s">
-        <v>89</v>
-      </c>
-      <c r="C40" t="s">
-        <v>99</v>
-      </c>
-      <c r="D40" t="s">
-        <v>145</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920356</v>
-      </c>
-      <c r="B41" t="s">
-        <v>89</v>
-      </c>
-      <c r="C41" t="s">
-        <v>99</v>
-      </c>
-      <c r="D41" t="s">
-        <v>145</v>
-      </c>
-      <c r="E41" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920356</v>
-      </c>
-      <c r="B42" t="s">
-        <v>89</v>
-      </c>
-      <c r="C42" t="s">
-        <v>99</v>
-      </c>
-      <c r="D42" t="s">
-        <v>145</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920021</v>
-      </c>
-      <c r="B43" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" t="s">
-        <v>116</v>
-      </c>
-      <c r="D43" t="s">
-        <v>146</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920023</v>
-      </c>
-      <c r="B44" t="s">
-        <v>91</v>
-      </c>
-      <c r="C44" t="s">
-        <v>78</v>
-      </c>
-      <c r="D44" t="s">
-        <v>147</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920023</v>
-      </c>
-      <c r="B45" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" t="s">
-        <v>78</v>
-      </c>
-      <c r="D45" t="s">
-        <v>147</v>
-      </c>
-      <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920023</v>
-      </c>
-      <c r="B46" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" t="s">
-        <v>78</v>
-      </c>
-      <c r="D46" t="s">
-        <v>147</v>
-      </c>
-      <c r="E46" t="s">
-        <v>5</v>
-      </c>
-      <c r="F46" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920025</v>
-      </c>
-      <c r="B47" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" t="s">
-        <v>117</v>
-      </c>
-      <c r="D47" t="s">
-        <v>148</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920025</v>
-      </c>
-      <c r="B48" t="s">
-        <v>92</v>
-      </c>
-      <c r="C48" t="s">
-        <v>117</v>
-      </c>
-      <c r="D48" t="s">
-        <v>148</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920026</v>
-      </c>
-      <c r="B49" t="s">
-        <v>93</v>
-      </c>
-      <c r="C49" t="s">
-        <v>78</v>
-      </c>
-      <c r="D49" t="s">
-        <v>149</v>
-      </c>
-      <c r="E49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920027</v>
-      </c>
-      <c r="B50" t="s">
-        <v>94</v>
-      </c>
-      <c r="C50" t="s">
-        <v>118</v>
-      </c>
-      <c r="D50" t="s">
-        <v>134</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920028</v>
-      </c>
-      <c r="B51" t="s">
-        <v>95</v>
-      </c>
-      <c r="C51" t="s">
-        <v>119</v>
-      </c>
-      <c r="D51" t="s">
-        <v>150</v>
-      </c>
-      <c r="E51" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920393</v>
-      </c>
-      <c r="B52" t="s">
-        <v>96</v>
-      </c>
-      <c r="C52" t="s">
-        <v>120</v>
-      </c>
-      <c r="D52" t="s">
-        <v>151</v>
-      </c>
-      <c r="E52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920393</v>
-      </c>
-      <c r="B53" t="s">
-        <v>96</v>
-      </c>
-      <c r="C53" t="s">
-        <v>120</v>
-      </c>
-      <c r="D53" t="s">
-        <v>151</v>
-      </c>
-      <c r="E53" t="s">
-        <v>6</v>
-      </c>
-      <c r="F53" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920393</v>
-      </c>
-      <c r="B54" t="s">
-        <v>96</v>
-      </c>
-      <c r="C54" t="s">
-        <v>120</v>
-      </c>
-      <c r="D54" t="s">
-        <v>151</v>
-      </c>
-      <c r="E54" t="s">
-        <v>5</v>
-      </c>
-      <c r="F54" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920393</v>
-      </c>
-      <c r="B55" t="s">
-        <v>96</v>
-      </c>
-      <c r="C55" t="s">
-        <v>120</v>
-      </c>
-      <c r="D55" t="s">
-        <v>151</v>
-      </c>
-      <c r="E55" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -5131,101 +4591,101 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920393</v>
+        <v>21330051920001</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920001</v>
+        <v>21330051920007</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920007</v>
+        <v>21330051920380</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920356</v>
+        <v>21330051920014</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920023</v>
+        <v>20330051920019</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920002</v>
+        <v>21330051920385</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -5233,186 +4693,186 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920005</v>
+        <v>21330051920002</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920006</v>
+        <v>21330051920003</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920049</v>
+        <v>21330051920005</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920380</v>
+        <v>21330051920006</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920355</v>
+        <v>21330051920010</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920014</v>
+        <v>21330051920355</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920019</v>
+        <v>21330051920013</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920017</v>
+        <v>21330051920015</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920385</v>
+        <v>21330051920017</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" t="s">
         <v>114</v>
       </c>
-      <c r="D16" t="s">
-        <v>143</v>
-      </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920025</v>
+        <v>20330051920022</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920003</v>
+        <v>21330051920356</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -5420,16 +4880,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920008</v>
+        <v>21330051920023</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -5437,16 +4897,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920010</v>
+        <v>21330051920026</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -5454,16 +4914,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920078</v>
+        <v>21330051920028</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -5471,16 +4931,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920011</v>
+        <v>21330051920393</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -5488,203 +4948,203 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920013</v>
+        <v>21330051920004</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="D23" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920391</v>
+        <v>21330051920008</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920015</v>
+        <v>20330051920049</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920016</v>
+        <v>20330051920078</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920022</v>
+        <v>21330051920011</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920379</v>
+        <v>21330051920012</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920018</v>
+        <v>20330051920391</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="D29" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920021</v>
+        <v>21330051920016</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920026</v>
+        <v>21330051920379</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="D31" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920027</v>
+        <v>21330051920018</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="D32" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920028</v>
+        <v>21330051920019</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="D33" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920004</v>
+        <v>21330051920021</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="C34" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -5692,16 +5152,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920012</v>
+        <v>21330051920022</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="D35" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -5709,16 +5169,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920019</v>
+        <v>21330051920025</v>
       </c>
       <c r="B36" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C36" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D36" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -5726,16 +5186,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920022</v>
+        <v>21330051920027</v>
       </c>
       <c r="B37" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="C37" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D37" t="s">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -5748,7 +5208,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5786,10 +5246,10 @@
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5798,7 +5258,7 @@
         <v>58</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -5809,10 +5269,10 @@
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -5826,16 +5286,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920049</v>
+        <v>21330051920355</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5844,21 +5304,21 @@
         <v>58</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920049</v>
+        <v>21330051920355</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -5872,16 +5332,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920355</v>
+        <v>21330051920018</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5890,44 +5350,44 @@
         <v>58</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920355</v>
+        <v>21330051920018</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920016</v>
+        <v>21330051920028</v>
       </c>
       <c r="B8" t="s">
         <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5941,16 +5401,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920016</v>
+        <v>21330051920028</v>
       </c>
       <c r="B9" t="s">
         <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -5964,62 +5424,62 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920022</v>
+        <v>21330051920003</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920022</v>
+        <v>20330051920049</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D11" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920018</v>
+        <v>21330051920010</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -6033,45 +5493,45 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920018</v>
+        <v>21330051920013</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920025</v>
+        <v>21330051920015</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -6079,16 +5539,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920025</v>
+        <v>20330051920022</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -6102,324 +5562,25 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920026</v>
+        <v>21330051920021</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="D16" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G16">
         <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920026</v>
-      </c>
-      <c r="B17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" t="s">
-        <v>149</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920003</v>
-      </c>
-      <c r="B18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" t="s">
-        <v>123</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920008</v>
-      </c>
-      <c r="B19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" t="s">
-        <v>127</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920010</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" t="s">
-        <v>130</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920078</v>
-      </c>
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" t="s">
-        <v>132</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920011</v>
-      </c>
-      <c r="B22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" t="s">
-        <v>106</v>
-      </c>
-      <c r="D22" t="s">
-        <v>133</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920013</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" t="s">
-        <v>107</v>
-      </c>
-      <c r="D23" t="s">
-        <v>134</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920391</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" t="s">
-        <v>137</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>57</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920015</v>
-      </c>
-      <c r="B25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" t="s">
-        <v>138</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>57</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920379</v>
-      </c>
-      <c r="B26" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" t="s">
-        <v>113</v>
-      </c>
-      <c r="D26" t="s">
-        <v>142</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>57</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920021</v>
-      </c>
-      <c r="B27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" t="s">
-        <v>116</v>
-      </c>
-      <c r="D27" t="s">
-        <v>146</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>57</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920027</v>
-      </c>
-      <c r="B28" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" t="s">
-        <v>134</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>57</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920028</v>
-      </c>
-      <c r="B29" t="s">
-        <v>95</v>
-      </c>
-      <c r="C29" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" t="s">
-        <v>150</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>57</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2AEV - Estadisticos 20212.xlsx
+++ b/grupos/2AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="161">
   <si>
     <t>Materia</t>
   </si>
@@ -197,15 +197,15 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -224,265 +224,265 @@
     <t>ACEVEDO</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>MONFIL</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>EDGAR FLORENCIO</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>JOSE DAMIAN</t>
+  </si>
+  <si>
+    <t>MARIA VALERIA</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>VICTOR ISRAEL</t>
+  </si>
+  <si>
+    <t>JOSE EDUARDO</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>ANGEL YAIR</t>
+  </si>
+  <si>
     <t>ANGELES</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>COBOS</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MACIEL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>TAMAYO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
   </si>
   <si>
     <t>ROCHA</t>
   </si>
   <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>MONFIL</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
+    <t>CANTU</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>JACOBO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>ATENOGENES</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
   </si>
   <si>
     <t>ADRIAN</t>
   </si>
   <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>EDGAR FLORENCIO</t>
-  </si>
-  <si>
-    <t>YOLET</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
+    <t>ITZEEL GUADALUPE</t>
+  </si>
+  <si>
+    <t>JUAN DIEGO</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>DULIAM</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>DAVID DANIEL</t>
   </si>
   <si>
     <t>YAIR</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
-    <t>LUIS ARMANDO</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>ANGEL YAIR</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MACIEL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>CANTU</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>ATENOGENES</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>ITZEEL GUADALUPE</t>
-  </si>
-  <si>
-    <t>JUAN DIEGO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>DAVID DANIEL</t>
   </si>
   <si>
     <t>MIGUEL</t>
@@ -986,7 +986,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -1004,7 +1004,7 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>5</v>
@@ -1016,46 +1016,46 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>-1</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1063,7 +1063,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -1081,7 +1081,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>5</v>
@@ -1093,31 +1093,31 @@
         <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>5</v>
@@ -1176,22 +1176,22 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
         <v>6</v>
@@ -1200,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>-1</v>
@@ -1235,7 +1235,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>5</v>
@@ -1247,28 +1247,28 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>6</v>
@@ -1286,7 +1286,7 @@
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1330,25 +1330,25 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>10</v>
@@ -1363,7 +1363,7 @@
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1389,7 +1389,7 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -1401,34 +1401,34 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>6</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>8</v>
@@ -1437,7 +1437,7 @@
         <v>-1</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1448,7 +1448,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -1466,7 +1466,7 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>5</v>
@@ -1478,31 +1478,31 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1514,10 +1514,10 @@
         <v>-1</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1561,22 +1561,22 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1594,7 +1594,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1638,28 +1638,28 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>9</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1671,7 +1671,7 @@
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1679,7 +1679,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>5</v>
@@ -1697,7 +1697,7 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>5</v>
@@ -1709,37 +1709,37 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>5</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>-1</v>
@@ -1792,22 +1792,22 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>6</v>
@@ -1863,43 +1863,43 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>-1</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1946,22 +1946,22 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1973,7 +1973,7 @@
         <v>7</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -2017,19 +2017,19 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -2038,7 +2038,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2088,25 +2088,25 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>6</v>
@@ -2159,37 +2159,37 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>6</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>-1</v>
@@ -2198,7 +2198,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2206,7 +2206,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>5</v>
@@ -2224,7 +2224,7 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>5</v>
@@ -2236,31 +2236,31 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
         <v>5</v>
@@ -2313,7 +2313,7 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>8</v>
@@ -2322,25 +2322,25 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
         <v>-1</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>6</v>
@@ -2349,10 +2349,10 @@
         <v>-1</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2396,22 +2396,22 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2420,10 +2420,10 @@
         <v>6</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2473,31 +2473,31 @@
         <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>8</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>-1</v>
@@ -2514,7 +2514,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>5</v>
@@ -2532,43 +2532,43 @@
         <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>5</v>
@@ -2627,22 +2627,22 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2654,7 +2654,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2704,22 +2704,22 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2734,7 +2734,7 @@
         <v>-1</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -2781,22 +2781,22 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -2808,13 +2808,13 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2822,7 +2822,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C28">
         <v>5</v>
@@ -2840,7 +2840,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
         <v>5</v>
@@ -2852,34 +2852,34 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>6</v>
@@ -2888,10 +2888,10 @@
         <v>-1</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2929,31 +2929,31 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>5</v>
@@ -3006,37 +3006,37 @@
         <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>6</v>
@@ -3045,7 +3045,7 @@
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3089,22 +3089,22 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -3166,28 +3166,28 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
         <v>10</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>8</v>
@@ -3199,7 +3199,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3243,22 +3243,22 @@
         <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3320,28 +3320,28 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q34">
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>7</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -3353,7 +3353,7 @@
         <v>10</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3397,34 +3397,34 @@
         <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>9</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3456,7 +3456,7 @@
         <v>6</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
         <v>5</v>
@@ -3468,31 +3468,31 @@
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M36">
         <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U36">
         <v>5</v>
@@ -3504,10 +3504,10 @@
         <v>-1</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3545,43 +3545,43 @@
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M37">
         <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q37">
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
         <v>6</v>
       </c>
       <c r="U37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W37">
         <v>-1</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y37">
         <v>6</v>
@@ -3628,22 +3628,22 @@
         <v>8</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>10</v>
@@ -3661,7 +3661,7 @@
         <v>10</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3699,34 +3699,34 @@
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M39">
         <v>6</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q39">
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T39">
         <v>9</v>
       </c>
       <c r="U39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V39">
         <v>6</v>
@@ -3738,7 +3738,7 @@
         <v>7</v>
       </c>
       <c r="Y39">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3835,19 +3835,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>77.78</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>22.22</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3858,28 +3858,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
       </c>
       <c r="C4">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>63.89</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G4">
-        <v>36.11</v>
+        <v>14.29</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -3899,57 +3899,57 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>86.11</v>
+      </c>
+      <c r="G5">
+        <v>13.89</v>
+      </c>
+      <c r="H5">
+        <v>7.1</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>77.78</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>8.4</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>22.22</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>82.86</v>
+        <v>88.89</v>
       </c>
       <c r="G6">
-        <v>17.14</v>
+        <v>8.33</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3963,19 +3963,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>91.67</v>
+        <v>94.44</v>
       </c>
       <c r="G7">
-        <v>8.33</v>
+        <v>5.56</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3991,7 +3991,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4026,10 +4026,10 @@
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4040,56 +4040,56 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920001</v>
+        <v>21330051920003</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920002</v>
+        <v>21330051920005</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920003</v>
+        <v>21330051920006</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4100,16 +4100,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920005</v>
+        <v>21330051920007</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4120,16 +4120,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920006</v>
+        <v>21330051920380</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
         <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4140,16 +4140,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920007</v>
+        <v>21330051920010</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
         <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4160,33 +4160,33 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920007</v>
+        <v>21330051920355</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
         <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920380</v>
+        <v>21330051920013</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
         <v>107</v>
@@ -4200,36 +4200,36 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920380</v>
+        <v>21330051920014</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920010</v>
+        <v>20330051920019</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4240,33 +4240,33 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920355</v>
+        <v>20330051920019</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
         <v>109</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920013</v>
+        <v>21330051920015</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
         <v>110</v>
@@ -4280,13 +4280,13 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920014</v>
+        <v>20330051920022</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
         <v>111</v>
@@ -4300,36 +4300,36 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920014</v>
+        <v>21330051920385</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920019</v>
+        <v>21330051920356</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -4340,36 +4340,36 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920019</v>
+        <v>21330051920023</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920015</v>
+        <v>21330051920026</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -4380,181 +4380,41 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920017</v>
+        <v>21330051920028</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
         <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E20" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920022</v>
+        <v>21330051920393</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920385</v>
-      </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" t="s">
-        <v>116</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920385</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" t="s">
-        <v>116</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920356</v>
-      </c>
-      <c r="B24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" t="s">
-        <v>88</v>
-      </c>
-      <c r="D24" t="s">
-        <v>117</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920023</v>
-      </c>
-      <c r="B25" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920026</v>
-      </c>
-      <c r="B26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" t="s">
-        <v>96</v>
-      </c>
-      <c r="D26" t="s">
-        <v>119</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920028</v>
-      </c>
-      <c r="B27" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" t="s">
-        <v>99</v>
-      </c>
-      <c r="D27" t="s">
-        <v>120</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920393</v>
-      </c>
-      <c r="B28" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" t="s">
-        <v>100</v>
-      </c>
-      <c r="D28" t="s">
-        <v>121</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4591,16 +4451,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920001</v>
+        <v>20330051920019</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -4608,101 +4468,101 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920007</v>
+        <v>21330051920001</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920380</v>
+        <v>21330051920003</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920014</v>
+        <v>21330051920005</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920019</v>
+        <v>21330051920006</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920385</v>
+        <v>21330051920007</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920002</v>
+        <v>21330051920380</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -4710,16 +4570,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920003</v>
+        <v>21330051920010</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4727,16 +4587,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920005</v>
+        <v>21330051920355</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4744,16 +4604,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920006</v>
+        <v>21330051920013</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -4761,13 +4621,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920010</v>
+        <v>21330051920014</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
         <v>108</v>
@@ -4778,16 +4638,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920355</v>
+        <v>21330051920015</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -4795,16 +4655,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920013</v>
+        <v>20330051920022</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -4812,16 +4672,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920015</v>
+        <v>21330051920385</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
         <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -4829,16 +4689,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920017</v>
+        <v>21330051920356</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -4846,16 +4706,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920022</v>
+        <v>21330051920023</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -4863,16 +4723,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920356</v>
+        <v>21330051920026</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -4880,16 +4740,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920023</v>
+        <v>21330051920028</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -4897,16 +4757,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920026</v>
+        <v>21330051920393</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -4914,47 +4774,47 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920028</v>
+        <v>21330051920002</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920393</v>
+        <v>21330051920004</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="D22" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920004</v>
+        <v>21330051920008</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="C23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D23" t="s">
         <v>147</v>
@@ -4965,13 +4825,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920008</v>
+        <v>20330051920049</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D24" t="s">
         <v>148</v>
@@ -4982,13 +4842,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920049</v>
+        <v>20330051920078</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
         <v>149</v>
@@ -4999,13 +4859,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920078</v>
+        <v>21330051920011</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="D26" t="s">
         <v>150</v>
@@ -5016,13 +4876,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920011</v>
+        <v>21330051920012</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>137</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
         <v>151</v>
@@ -5033,13 +4893,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920012</v>
+        <v>20330051920391</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="D28" t="s">
         <v>152</v>
@@ -5050,13 +4910,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920391</v>
+        <v>21330051920016</v>
       </c>
       <c r="B29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D29" t="s">
         <v>153</v>
@@ -5067,13 +4927,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920016</v>
+        <v>21330051920017</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="D30" t="s">
         <v>154</v>
@@ -5087,10 +4947,10 @@
         <v>21330051920379</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C31" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D31" t="s">
         <v>155</v>
@@ -5104,10 +4964,10 @@
         <v>21330051920018</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C32" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D32" t="s">
         <v>156</v>
@@ -5121,10 +4981,10 @@
         <v>21330051920019</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D33" t="s">
         <v>157</v>
@@ -5138,10 +4998,10 @@
         <v>21330051920021</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C34" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D34" t="s">
         <v>158</v>
@@ -5155,10 +5015,10 @@
         <v>21330051920022</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C35" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D35" t="s">
         <v>159</v>
@@ -5172,10 +5032,10 @@
         <v>21330051920025</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D36" t="s">
         <v>160</v>
@@ -5189,13 +5049,13 @@
         <v>21330051920027</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C37" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D37" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -5208,7 +5068,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5240,16 +5100,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920005</v>
+        <v>21330051920006</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5263,16 +5123,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920005</v>
+        <v>21330051920006</v>
       </c>
       <c r="B3" t="s">
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -5286,16 +5146,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920355</v>
+        <v>21330051920007</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5309,16 +5169,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920355</v>
+        <v>21330051920007</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -5332,62 +5192,62 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920018</v>
+        <v>20330051920019</v>
       </c>
       <c r="B6" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920018</v>
+        <v>20330051920019</v>
       </c>
       <c r="B7" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920028</v>
+        <v>21330051920026</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5401,16 +5261,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920028</v>
+        <v>21330051920026</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -5424,16 +5284,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920003</v>
+        <v>21330051920001</v>
       </c>
       <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" t="s">
         <v>69</v>
       </c>
-      <c r="C10" t="s">
-        <v>87</v>
-      </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -5447,39 +5307,39 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920049</v>
+        <v>21330051920003</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920010</v>
+        <v>21330051920005</v>
       </c>
       <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
         <v>74</v>
       </c>
-      <c r="C12" t="s">
-        <v>91</v>
-      </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -5493,16 +5353,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920013</v>
+        <v>21330051920010</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -5516,16 +5376,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920015</v>
+        <v>21330051920355</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -5539,16 +5399,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920022</v>
+        <v>21330051920013</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -5562,16 +5422,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920021</v>
+        <v>21330051920015</v>
       </c>
       <c r="B16" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -5580,7 +5440,145 @@
         <v>57</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920022</v>
+      </c>
+      <c r="B17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920385</v>
+      </c>
+      <c r="B18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920021</v>
+      </c>
+      <c r="B19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920023</v>
+      </c>
+      <c r="B20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920028</v>
+      </c>
+      <c r="B21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920393</v>
+      </c>
+      <c r="B22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>57</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2AEV - Estadisticos 20212.xlsx
+++ b/grupos/2AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="161">
   <si>
     <t>Materia</t>
   </si>
@@ -224,6 +224,9 @@
     <t>ACEVEDO</t>
   </si>
   <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
@@ -236,6 +239,12 @@
     <t>COBOS</t>
   </si>
   <si>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
     <t>DIAZ</t>
   </si>
   <si>
@@ -245,45 +254,90 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>JUAREZ</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MACIEL</t>
+  </si>
+  <si>
     <t>MIXCOA</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>PACHECO</t>
   </si>
   <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
     <t>PELLICO</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
+    <t>TAMAYO</t>
+  </si>
+  <si>
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
     <t>URBINA</t>
   </si>
   <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>CANTU</t>
   </si>
   <si>
     <t>NOLASCO</t>
   </si>
   <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
     <t>MONFIL</t>
   </si>
   <si>
@@ -293,6 +347,9 @@
     <t>GASPAR</t>
   </si>
   <si>
+    <t>JACOBO</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
@@ -302,15 +359,39 @@
     <t>ENRIQUEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>VILLA</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>ROSETE</t>
   </si>
   <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>ATENOGENES</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
@@ -320,9 +401,15 @@
     <t>ALDAHIR</t>
   </si>
   <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
     <t>LUIS EDUARDO</t>
   </si>
   <si>
+    <t>ITZEEL GUADALUPE</t>
+  </si>
+  <si>
     <t>KEVIN ISAAC</t>
   </si>
   <si>
@@ -332,6 +419,12 @@
     <t>YOLET</t>
   </si>
   <si>
+    <t>JUAN DIEGO</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
     <t>ERNESTO</t>
   </si>
   <si>
@@ -341,6 +434,15 @@
     <t>MARIA VALERIA</t>
   </si>
   <si>
+    <t>DULIAM</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
     <t>OMAR</t>
   </si>
   <si>
@@ -350,21 +452,48 @@
     <t>ABRIL</t>
   </si>
   <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
     <t>VICTOR ISRAEL</t>
   </si>
   <si>
+    <t>DAVID DANIEL</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
     <t>JOSE EDUARDO</t>
   </si>
   <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
     <t>LUIS ARMANDO</t>
   </si>
   <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
     <t>OSCAR</t>
   </si>
   <si>
+    <t>GERSON UZIEL</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
     <t>NEMESIO NAHIM</t>
   </si>
   <si>
+    <t>JOSMAR JAHIR</t>
+  </si>
+  <si>
     <t>OSVALDO</t>
   </si>
   <si>
@@ -372,135 +501,6 @@
   </si>
   <si>
     <t>ANGEL YAIR</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MACIEL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>CANTU</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>ATENOGENES</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ITZEEL GUADALUPE</t>
-  </si>
-  <si>
-    <t>JUAN DIEGO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>DAVID DANIEL</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>GERSON UZIEL</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>JOSMAR JAHIR</t>
   </si>
 </sst>
 </file>
@@ -995,7 +995,7 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F4">
         <v>10</v>
@@ -1013,7 +1013,7 @@
         <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -1031,7 +1031,7 @@
         <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
         <v>6</v>
@@ -1049,7 +1049,7 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -1108,7 +1108,7 @@
         <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>5</v>
@@ -1149,7 +1149,7 @@
         <v>8</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -1167,7 +1167,7 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -1185,7 +1185,7 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
         <v>10</v>
@@ -1203,7 +1203,7 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1226,7 +1226,7 @@
         <v>6</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -1244,7 +1244,7 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
         <v>7</v>
@@ -1280,7 +1280,7 @@
         <v>6</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1380,7 +1380,7 @@
         <v>7</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F9">
         <v>9</v>
@@ -1398,7 +1398,7 @@
         <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1416,7 +1416,7 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
         <v>10</v>
@@ -1434,7 +1434,7 @@
         <v>8</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1457,7 +1457,7 @@
         <v>7</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>10</v>
@@ -1475,7 +1475,7 @@
         <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -1493,7 +1493,7 @@
         <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>6</v>
@@ -1511,7 +1511,7 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1688,7 +1688,7 @@
         <v>5</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -1706,7 +1706,7 @@
         <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -1724,7 +1724,7 @@
         <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
         <v>5</v>
@@ -1742,7 +1742,7 @@
         <v>6</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X13">
         <v>5</v>
@@ -1765,7 +1765,7 @@
         <v>7</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F14">
         <v>9</v>
@@ -1783,7 +1783,7 @@
         <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -1801,7 +1801,7 @@
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>10</v>
@@ -1819,7 +1819,7 @@
         <v>7</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1842,7 +1842,7 @@
         <v>8</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F15">
         <v>9</v>
@@ -1860,7 +1860,7 @@
         <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>10</v>
@@ -1878,7 +1878,7 @@
         <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>10</v>
@@ -1896,7 +1896,7 @@
         <v>7</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -2138,7 +2138,7 @@
         <v>7</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F19">
         <v>10</v>
@@ -2156,7 +2156,7 @@
         <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -2174,7 +2174,7 @@
         <v>6</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
         <v>10</v>
@@ -2192,7 +2192,7 @@
         <v>6</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>10</v>
@@ -2215,7 +2215,7 @@
         <v>7</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -2233,7 +2233,7 @@
         <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -2251,7 +2251,7 @@
         <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
         <v>5</v>
@@ -2269,7 +2269,7 @@
         <v>7</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>5</v>
@@ -2283,7 +2283,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -2292,7 +2292,7 @@
         <v>6</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F21">
         <v>9</v>
@@ -2301,7 +2301,7 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -2310,7 +2310,7 @@
         <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -2319,7 +2319,7 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>8</v>
@@ -2328,7 +2328,7 @@
         <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
         <v>10</v>
@@ -2337,7 +2337,7 @@
         <v>6</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>6</v>
@@ -2346,7 +2346,7 @@
         <v>6</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X21">
         <v>10</v>
@@ -2446,7 +2446,7 @@
         <v>8</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F23">
         <v>10</v>
@@ -2464,7 +2464,7 @@
         <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -2482,7 +2482,7 @@
         <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>10</v>
@@ -2500,7 +2500,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2559,7 +2559,7 @@
         <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
         <v>5</v>
@@ -2677,7 +2677,7 @@
         <v>8</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F26">
         <v>8</v>
@@ -2695,7 +2695,7 @@
         <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>8</v>
@@ -2713,7 +2713,7 @@
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
         <v>10</v>
@@ -2731,7 +2731,7 @@
         <v>8</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2831,7 +2831,7 @@
         <v>6</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -2849,7 +2849,7 @@
         <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>8</v>
@@ -2867,7 +2867,7 @@
         <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
         <v>8</v>
@@ -2885,7 +2885,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X28">
         <v>7</v>
@@ -2908,7 +2908,7 @@
         <v>6</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -2926,7 +2926,7 @@
         <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -2944,7 +2944,7 @@
         <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
         <v>5</v>
@@ -2962,7 +2962,7 @@
         <v>6</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>5</v>
@@ -3293,7 +3293,7 @@
         <v>8</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F34">
         <v>10</v>
@@ -3311,7 +3311,7 @@
         <v>6</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -3329,7 +3329,7 @@
         <v>6</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
         <v>10</v>
@@ -3347,7 +3347,7 @@
         <v>7</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -3447,7 +3447,7 @@
         <v>7</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F36">
         <v>10</v>
@@ -3465,7 +3465,7 @@
         <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L36">
         <v>8</v>
@@ -3483,7 +3483,7 @@
         <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R36">
         <v>7</v>
@@ -3501,7 +3501,7 @@
         <v>7</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X36">
         <v>8</v>
@@ -3524,7 +3524,7 @@
         <v>8</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F37">
         <v>10</v>
@@ -3542,7 +3542,7 @@
         <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L37">
         <v>7</v>
@@ -3560,7 +3560,7 @@
         <v>7</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R37">
         <v>10</v>
@@ -3578,7 +3578,7 @@
         <v>7</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X37">
         <v>9</v>
@@ -3678,7 +3678,7 @@
         <v>6</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F39">
         <v>7</v>
@@ -3696,7 +3696,7 @@
         <v>6</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L39">
         <v>7</v>
@@ -3714,7 +3714,7 @@
         <v>6</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R39">
         <v>8</v>
@@ -3732,7 +3732,7 @@
         <v>6</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X39">
         <v>7</v>
@@ -3803,25 +3803,25 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>38.89</v>
+        <v>63.89</v>
       </c>
       <c r="G2">
-        <v>8.33</v>
+        <v>36.11</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>52.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3934,22 +3934,22 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
         <v>88.89</v>
       </c>
       <c r="G6">
-        <v>8.33</v>
+        <v>11.11</v>
       </c>
       <c r="H6">
         <v>7.7</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3991,7 +3991,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4016,406 +4016,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920001</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920003</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920005</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920006</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920007</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920380</v>
-      </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920010</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8" t="s">
-        <v>105</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920355</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920013</v>
-      </c>
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" t="s">
-        <v>107</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920014</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920019</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920019</v>
-      </c>
-      <c r="B13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" t="s">
-        <v>109</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920015</v>
-      </c>
-      <c r="B14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" t="s">
-        <v>110</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920022</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" t="s">
-        <v>111</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920385</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920356</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920023</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920026</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" t="s">
-        <v>115</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920028</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" t="s">
-        <v>116</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920393</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" t="s">
-        <v>117</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4451,36 +4051,36 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920019</v>
+        <v>21330051920001</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920001</v>
+        <v>21330051920002</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4488,299 +4088,299 @@
         <v>21330051920003</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920005</v>
+        <v>21330051920004</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920006</v>
+        <v>21330051920005</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920007</v>
+        <v>21330051920006</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920380</v>
+        <v>21330051920007</v>
       </c>
       <c r="B8" t="s">
         <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920010</v>
+        <v>21330051920008</v>
       </c>
       <c r="B9" t="s">
         <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920355</v>
+        <v>20330051920049</v>
       </c>
       <c r="B10" t="s">
         <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920013</v>
+        <v>21330051920380</v>
       </c>
       <c r="B11" t="s">
         <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920014</v>
+        <v>21330051920010</v>
       </c>
       <c r="B12" t="s">
         <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920015</v>
+        <v>21330051920355</v>
       </c>
       <c r="B13" t="s">
         <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920022</v>
+        <v>20330051920078</v>
       </c>
       <c r="B14" t="s">
         <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920385</v>
+        <v>21330051920011</v>
       </c>
       <c r="B15" t="s">
         <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920356</v>
+        <v>21330051920012</v>
       </c>
       <c r="B16" t="s">
         <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920023</v>
+        <v>21330051920013</v>
       </c>
       <c r="B17" t="s">
         <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920026</v>
+        <v>21330051920014</v>
       </c>
       <c r="B18" t="s">
         <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920028</v>
+        <v>20330051920019</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="D19" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920393</v>
+        <v>20330051920391</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920002</v>
+        <v>21330051920015</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
         <v>145</v>
@@ -4791,13 +4391,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920004</v>
+        <v>21330051920016</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
         <v>146</v>
@@ -4808,13 +4408,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920008</v>
+        <v>21330051920017</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
         <v>147</v>
@@ -4825,13 +4425,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920049</v>
+        <v>20330051920022</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
         <v>148</v>
@@ -4842,13 +4442,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920078</v>
+        <v>21330051920379</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
         <v>149</v>
@@ -4859,13 +4459,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920011</v>
+        <v>21330051920385</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
         <v>150</v>
@@ -4876,13 +4476,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920012</v>
+        <v>21330051920018</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
         <v>151</v>
@@ -4893,13 +4493,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920391</v>
+        <v>21330051920356</v>
       </c>
       <c r="B28" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s">
         <v>152</v>
@@ -4910,13 +4510,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920016</v>
+        <v>21330051920019</v>
       </c>
       <c r="B29" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
         <v>153</v>
@@ -4927,13 +4527,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920017</v>
+        <v>21330051920021</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
         <v>154</v>
@@ -4944,13 +4544,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920379</v>
+        <v>21330051920022</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
         <v>155</v>
@@ -4961,13 +4561,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920018</v>
+        <v>21330051920023</v>
       </c>
       <c r="B32" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="D32" t="s">
         <v>156</v>
@@ -4978,13 +4578,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920019</v>
+        <v>21330051920025</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s">
         <v>157</v>
@@ -4995,13 +4595,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920021</v>
+        <v>21330051920026</v>
       </c>
       <c r="B34" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
         <v>158</v>
@@ -5012,16 +4612,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920022</v>
+        <v>21330051920027</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="D35" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -5029,16 +4629,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920025</v>
+        <v>21330051920028</v>
       </c>
       <c r="B36" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="C36" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="D36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -5046,16 +4646,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920027</v>
+        <v>21330051920393</v>
       </c>
       <c r="B37" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="D37" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -5068,7 +4668,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5103,13 +4703,13 @@
         <v>21330051920006</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5126,13 +4726,13 @@
         <v>21330051920006</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -5141,7 +4741,7 @@
         <v>57</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -5149,13 +4749,13 @@
         <v>21330051920007</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5172,13 +4772,13 @@
         <v>21330051920007</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -5187,7 +4787,7 @@
         <v>57</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -5195,13 +4795,13 @@
         <v>20330051920019</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5210,7 +4810,7 @@
         <v>61</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -5218,13 +4818,13 @@
         <v>20330051920019</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -5233,7 +4833,7 @@
         <v>57</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -5241,13 +4841,13 @@
         <v>21330051920026</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>158</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5264,13 +4864,13 @@
         <v>21330051920026</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>158</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -5279,21 +4879,21 @@
         <v>57</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920001</v>
+        <v>21330051920003</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -5302,21 +4902,21 @@
         <v>57</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920003</v>
+        <v>21330051920385</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -5325,21 +4925,21 @@
         <v>57</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920005</v>
+        <v>21330051920021</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -5348,21 +4948,21 @@
         <v>57</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920010</v>
+        <v>21330051920028</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>159</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -5371,214 +4971,7 @@
         <v>57</v>
       </c>
       <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920355</v>
-      </c>
-      <c r="B14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920013</v>
-      </c>
-      <c r="B15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920015</v>
-      </c>
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" t="s">
-        <v>110</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920022</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>95</v>
-      </c>
-      <c r="D17" t="s">
-        <v>111</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920385</v>
-      </c>
-      <c r="B18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" t="s">
-        <v>112</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920021</v>
-      </c>
-      <c r="B19" t="s">
-        <v>127</v>
-      </c>
-      <c r="C19" t="s">
-        <v>141</v>
-      </c>
-      <c r="D19" t="s">
-        <v>158</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920023</v>
-      </c>
-      <c r="B20" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" t="s">
-        <v>114</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920028</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" t="s">
-        <v>116</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920393</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" t="s">
-        <v>117</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
